--- a/AAII_Financials/Quarterly/BAP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="92">
   <si>
     <t>BAP</t>
   </si>
@@ -656,344 +656,351 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1714000</v>
+        <v>1683500</v>
       </c>
       <c r="E8" s="3">
+        <v>1627800</v>
+      </c>
+      <c r="F8" s="3">
         <v>1603200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1526300</v>
       </c>
-      <c r="G8" s="3">
-        <v>1492800</v>
-      </c>
       <c r="H8" s="3">
-        <v>1300000</v>
+        <v>1450200</v>
       </c>
       <c r="I8" s="3">
+        <v>1290400</v>
+      </c>
+      <c r="J8" s="3">
         <v>1362300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1232400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1120600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1123900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1099900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1066100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1110600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1072700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1156500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1061700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>950500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>864400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>841200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>828700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>767500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>747500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>704300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>785500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>737300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>780500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>775000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>817600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>825800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>833300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>849800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>840100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>833400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>826700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>831500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>834900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>819000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>826200</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>858900</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>819000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E9" s="3">
         <v>8100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>17000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>13500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>11600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6900</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1069,53 +1076,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1705900</v>
+        <v>1672700</v>
       </c>
       <c r="E10" s="3">
+        <v>1619700</v>
+      </c>
+      <c r="F10" s="3">
         <v>1586200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1513700</v>
       </c>
-      <c r="G10" s="3">
-        <v>1482100</v>
-      </c>
       <c r="H10" s="3">
-        <v>1291400</v>
+        <v>1439500</v>
       </c>
       <c r="I10" s="3">
+        <v>1281800</v>
+      </c>
+      <c r="J10" s="3">
         <v>1348800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1222700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1111600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1115200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1086500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1054400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1100200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1065900</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1191,8 +1201,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,52 +1496,55 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>-25500</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>84700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>6200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>45200</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1601,130 +1621,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E15" s="3">
         <v>57100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>24400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8700</v>
       </c>
-      <c r="G15" s="3">
-        <v>8000</v>
-      </c>
       <c r="H15" s="3">
+        <v>49700</v>
+      </c>
+      <c r="I15" s="3">
         <v>46400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>42800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>19100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>54500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>37200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>40000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>32700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>33900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>32700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-74500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-46200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-46000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-44800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-49400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-46400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-43500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-44300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-41300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-44700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-46300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-42400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-30700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-48600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-42500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-36500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-30900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-30700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-31500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-34600</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-22300</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-34600</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>-34400</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-34900</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>-20100</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>-34900</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>877800</v>
+        <v>851800</v>
       </c>
       <c r="E17" s="3">
+        <v>791700</v>
+      </c>
+      <c r="F17" s="3">
         <v>914400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>804800</v>
       </c>
-      <c r="G17" s="3">
-        <v>777900</v>
-      </c>
       <c r="H17" s="3">
-        <v>612800</v>
+        <v>726600</v>
       </c>
       <c r="I17" s="3">
+        <v>603100</v>
+      </c>
+      <c r="J17" s="3">
         <v>778900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>668000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>644500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>567300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>671500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>620200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>594900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>562100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>603500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>385200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>302700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>244100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>201500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>207400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>251100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>331900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>356100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>557900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>893900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>524500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>321600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>353100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>342700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>329700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>335400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>345600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>315000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>331100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>354700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>338500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>354700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>380900</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>364200</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>343400</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>831700</v>
+      </c>
+      <c r="E18" s="3">
         <v>836200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>688800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>721500</v>
       </c>
-      <c r="G18" s="3">
-        <v>715000</v>
-      </c>
       <c r="H18" s="3">
+        <v>723600</v>
+      </c>
+      <c r="I18" s="3">
         <v>687300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>583300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>564400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>476100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>556600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>428400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>445900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>515600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>510600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>553100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>676500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>647700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>620300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>639700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>621300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>516500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>415600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>348300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>227600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-156600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>256000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>453400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>464500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>483200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>503600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>514400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>494500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>518400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>495600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>476800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>496400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>464200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>445300</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>494700</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>475600</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,252 +2085,259 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3">
         <v>12800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1500</v>
       </c>
-      <c r="G20" s="3">
-        <v>-8700</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3">
         <v>33100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-9600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-15900</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>36600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-17500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-132200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-168200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-194500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-154200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-215500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-181700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-213700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-146300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-147800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-187200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-128900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-167500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-118000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-66800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-72100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-74600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-133000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-88800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-107600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-66000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-44600</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-9600</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-82300</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-72800</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-123800</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-77900</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>848000</v>
+      </c>
+      <c r="E21" s="3">
         <v>893300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>700400</v>
-      </c>
-      <c r="F21" s="3">
-        <v>731700</v>
       </c>
       <c r="G21" s="3">
         <v>731700</v>
       </c>
       <c r="H21" s="3">
+        <v>773400</v>
+      </c>
+      <c r="I21" s="3">
         <v>733700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>593000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>593100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>546500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>593900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>431700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>487000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>567100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>540000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>455200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>554400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>499300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>511000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>475500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>486000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>346300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>313600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>243600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>85200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-239200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>130900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>366100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>446200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>461900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>465500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>404400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>444600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>439400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>464200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>454500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>521500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>416300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>407400</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>390900</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>432600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2340,8 +2380,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2418,252 +2458,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>831700</v>
+      </c>
+      <c r="E23" s="3">
         <v>836200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>701500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>723000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>723600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>687300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>465500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>567800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>492100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>556600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>346500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>454400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>533100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>507200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>420800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>508200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>453200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>466100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>424200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>439600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>302800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>269400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>200400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>40500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-285500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>88600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>335400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>397700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>411100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>429000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>381400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>405700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>410800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>429700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>432100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>486900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>382000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>372500</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>370900</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>397800</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>238500</v>
+      </c>
+      <c r="E24" s="3">
         <v>231700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>218500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>210100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>196900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>192200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>158600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>149300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>135400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>142100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>117000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>120500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>139000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>131200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>126300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>153100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>139800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>148800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>128400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>116300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>112400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>89600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>27000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>14800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-112100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>36000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>92800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>105700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>111000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>117200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>107700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>105700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>115000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>114200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>110000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>112000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>97900</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>98200</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>92900</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>102400</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>593200</v>
+      </c>
+      <c r="E26" s="3">
         <v>604500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>483000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>513000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>526700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>495100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>306900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>418500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>356600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>414600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>229500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>333900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>394100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>376000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>294600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>355100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>313400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>317300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>295800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>323300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>190300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>179700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>173500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>25700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-173400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>52600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>242500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>292000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>300100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>311800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>273700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>300000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>295800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>315500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>322100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>374800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>284000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>274300</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>278000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>295400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>580400</v>
+      </c>
+      <c r="E27" s="3">
         <v>591000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>471700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>501500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>514700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>485000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>298700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>409800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>349200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>406400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>226700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>327200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>386200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>368000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>288100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>346700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>305700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>309800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>288600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>316100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>185700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>175400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>170300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>27800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-167700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>51600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>237600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>286100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>294200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>305600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>268100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>294300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>289700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>307500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>315200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>367400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>277500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>268300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>271100</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>287700</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3">
         <v>-12800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1500</v>
       </c>
-      <c r="G32" s="3">
-        <v>8700</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3">
         <v>-33100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>9600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>15900</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>-36600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>17500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>132200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>168200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>194500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>154200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>215500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>181700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>213700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>146300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>147800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>187200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>128900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>167500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>118000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>66800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>72100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>74600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>133000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>88800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>107600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>66000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>44600</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>9600</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>82300</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>72800</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>123800</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>77900</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>580400</v>
+      </c>
+      <c r="E33" s="3">
         <v>591000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>471700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>501500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>514700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>485000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>298700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>409800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>349200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>406400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>226700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>327200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>386200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>368000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>288100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>346700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>305700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>309800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>288600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>316100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>185700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>175400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>170300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>27800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-167700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>51600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>237600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>286100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>294200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>305600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>268100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>294300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>289700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>307500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>315200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>367400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>277500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>268300</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>271100</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>287700</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>580400</v>
+      </c>
+      <c r="E35" s="3">
         <v>591000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>471700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>501500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>514700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>485000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>298700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>409800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>349200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>406400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>226700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>327200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>386200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>368000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>288100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>346700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>305700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>309800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>288600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>316100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>185700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>175400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>170300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>27800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-167700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>51600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>237600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>286100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>294200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>305600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>268100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>294300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>289700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>307500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>315200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>367400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>277500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>268300</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>271100</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>287700</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,297 +4305,304 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>14501400</v>
+        <v>5933100</v>
       </c>
       <c r="E41" s="3">
+        <v>6395600</v>
+      </c>
+      <c r="F41" s="3">
         <v>6715200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5727600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5585700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5660200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5321200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4494500</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M41" s="3">
         <v>10527100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1844600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3501900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9148400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3512200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9063200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9648500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8405900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9894700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10698000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>12089200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10075700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10422400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9576700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9345300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>9763700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6500600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>12695100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6908700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6384500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6140900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6210300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6813200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>7357400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>6386600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>6880900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>8256700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>6608400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>5928500</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>5041800</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>8328900</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5487800</v>
+      </c>
+      <c r="E42" s="3">
         <v>6088900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2451100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4349700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4433000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5092800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1833700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1366000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>1429200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1929900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2080300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1460400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3790700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2001400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1693900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1581100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1722000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>2545800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2417300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2196500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2489500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2625600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2136800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1856700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1580000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2254900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1452900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1470900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1501200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>2342400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1326800</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1672300</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>2659900</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>3617100</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1510900</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>1657700</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>1833600</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>4523600</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>1795300</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2023900</v>
+      </c>
+      <c r="E43" s="3">
         <v>2437200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2127300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1763100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2404900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1706200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>850700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1572500</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N43" s="3">
         <v>566700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>998100</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P43" s="3">
+      <c r="P43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q43" s="3">
         <v>252700</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4585,52 +4678,55 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E44" s="3">
         <v>23100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>26800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>27400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>26100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>26000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>44100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>26200</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N44" s="3">
         <v>29000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>30100</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4707,53 +4803,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2467900</v>
+      </c>
+      <c r="E45" s="3">
         <v>867100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>641400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2358200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1589300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1732800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>656300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1434100</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M45" s="3">
         <v>86700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>696900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>643000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>575900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1106200</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4829,53 +4928,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>24224800</v>
+      </c>
+      <c r="E46" s="3">
         <v>23936500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>19910600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>20929400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>20169200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>20707500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16116200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16292700</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M46" s="3">
         <v>12453300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12523400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12657800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11184600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14483100</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4951,374 +5053,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>11689500</v>
+      </c>
+      <c r="E47" s="3">
         <v>10546000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>12365100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>10511100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>10331300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>10155100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>11368300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>13166500</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M47" s="3">
         <v>13118800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>11161300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9957500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>12183300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>9092700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>192700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>175900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>173400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>171400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>179200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>176000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>166600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>164700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>168300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>167000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>169500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>152500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>153600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>158000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>154400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>159400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>163100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>214200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>211800</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>208900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>210000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>208300</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>202400</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>205000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>211900</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>195700</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>760900</v>
+      </c>
+      <c r="E48" s="3">
         <v>760800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>794400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>786000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>747500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>731600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>488200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>493900</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M48" s="3">
         <v>488100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>500100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>463200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>482100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>475100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>901500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>616000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>631900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>636400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>907000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>647200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>640600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>654500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>846200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>677200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>697000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>656000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1463400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>882000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>898800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>941700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>952900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>445700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>606000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>610400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>583200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>492000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>645300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>654300</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>622900</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>677800</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1418100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1354600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1416200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1325700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1255600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1205900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>872100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>851700</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>849900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>868600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>824100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>839800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>782300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>768700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>736600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>743800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>736600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>737300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>728500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>702800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>690000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>687700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>658200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>669000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>598100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>618500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>549500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>552100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>569300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>575900</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI49" s="3">
+      <c r="AI49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>582700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>584500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>586400</v>
       </c>
-      <c r="AL49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM49" s="3">
+      <c r="AM49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN49" s="3">
         <v>573500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>577900</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>593900</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>575900</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>217400</v>
+      </c>
+      <c r="E52" s="3">
         <v>1520600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2386800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>558100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>185300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>171200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2287300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>293200</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M52" s="3">
         <v>2275400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2186200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2656300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2800000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2429900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>300900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>293500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>296200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>321000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>320300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>427600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>437100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>444700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>441300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>463900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>406000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>198700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>127200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>112800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>113700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>114500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>129900</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI52" s="3">
+      <c r="AI52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>147200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>175300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>142200</v>
       </c>
-      <c r="AL52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM52" s="3">
+      <c r="AM52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN52" s="3">
         <v>165600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>164900</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>153300</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>240500</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>82824200</v>
+      </c>
+      <c r="E54" s="3">
         <v>79782800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>79472800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>73635200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>70351500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>69351600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>67899300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>67161400</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M54" s="3">
         <v>64834600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>64316700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>63014300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>64668900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>63363900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>62415400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>64923200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>64465800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>64825500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>66615500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>68323900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>65040300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>64844500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>61860900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>61619200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>59883800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>48768700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>45886500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>48761400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>48519600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>49479900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>49658500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>49017200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>49530400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>50533800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>50512600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>49861800</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>48986200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>48162000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>47382700</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>48041100</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,169 +6145,173 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>51597000</v>
+        <v>56469400</v>
       </c>
       <c r="E57" s="3">
+        <v>53574000</v>
+      </c>
+      <c r="F57" s="3">
         <v>51150100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>49482300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>47533100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>44161500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>43198800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>42664200</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M57" s="3">
         <v>39379900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>40027600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>39415000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>39521400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>39194700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>545700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5131300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5934000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6024900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>625600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7810000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>7833200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>8080900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>534100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>8254500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>7119900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2739400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>989300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2888800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3453300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3053300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3095600</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI57" s="3">
+      <c r="AI57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>3504500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>4539700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>555600</v>
       </c>
-      <c r="AL57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM57" s="3">
+      <c r="AM57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN57" s="3">
         <v>4589100</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>4648600</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>4582100</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>5112300</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3404400</v>
+      </c>
+      <c r="E58" s="3">
         <v>2292300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2161400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2472200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2470700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2461900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3145500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3303900</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>3735500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1453500</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -6259,175 +6393,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3756200</v>
+        <v>1619800</v>
       </c>
       <c r="E59" s="3">
+        <v>1779200</v>
+      </c>
+      <c r="F59" s="3">
         <v>705000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1404900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1297100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3484400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>468800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2959400</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M59" s="3">
         <v>169800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>566200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>427800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>176400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>242800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>548000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>105000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>42000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>50200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>337000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>48300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>20200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>40800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>236700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>60800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>41500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>85400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>343200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>105800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>86700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>133400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>189700</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI59" s="3">
+      <c r="AI59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>59700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>115100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>142500</v>
       </c>
-      <c r="AL59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM59" s="3">
+      <c r="AM59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN59" s="3">
         <v>30000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>300</v>
       </c>
-      <c r="AO59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AP59" s="3">
+      <c r="AP59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ59" s="3">
         <v>15300</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>61864000</v>
+      </c>
+      <c r="E60" s="3">
         <v>58121000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>54833000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>53699200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>51518500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>50368700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>47506500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>49278900</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M60" s="3">
         <v>39918500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>45005700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>41959200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>39697800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>39757700</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6503,252 +6643,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4729600</v>
+      </c>
+      <c r="E61" s="3">
         <v>5357600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8124800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4699500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4582800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4829100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7011400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4607500</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>10139500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6617700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8805900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10640500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9624400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7032000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6810300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6251800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6082700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6989900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6781400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6129000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6154100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6005700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6108200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6912200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6168400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6013300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6699800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6407100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6240500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>6543600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>6606400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>6916200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>6643400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>7182300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>7268300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>6996300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>6878500</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>4827900</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>5421100</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>365000</v>
+      </c>
+      <c r="E62" s="3">
         <v>396800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4781800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>284200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>386800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>379200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4091800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>512700</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M62" s="3">
         <v>5519000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3749100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3798900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5885800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5757200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>360000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>337600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>343700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>365700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>357200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>355900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>332100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>307500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>301400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>283700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>258000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>211200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>396100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>218900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>223100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>214900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>227800</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI62" s="3">
+      <c r="AI62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>255100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>265500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>81700</v>
       </c>
-      <c r="AL62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM62" s="3">
+      <c r="AM62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN62" s="3">
         <v>259500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>263200</v>
       </c>
-      <c r="AO62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AP62" s="3">
+      <c r="AP62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ62" s="3">
         <v>258500</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>71461400</v>
+      </c>
+      <c r="E66" s="3">
         <v>68138800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>67851600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>62889700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>60442900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>59417700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>58625400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>57997900</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M66" s="3">
         <v>55577100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>55401400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>54582600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>56224100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>55139300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>54725600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>57707600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>57333300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>57503000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>59406500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>61481100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>58384700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>58333300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>55360800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>55344000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>53558900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>43043600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>39477600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>41956300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>41764700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>42902500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>42980200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>42322900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>43044400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>44218800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>44066000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>43238400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>42713400</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>42221500</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>41429000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>42250800</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10725200</v>
+      </c>
+      <c r="E72" s="3">
         <v>11053900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2055700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>10083000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9378300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9432400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1496100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1214300</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M72" s="3">
         <v>1635600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1231300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>983500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>682600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7823600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7333700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7254100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7065900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7080200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6780100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6477300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6121400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5933500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5674400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5612600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5670100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5321800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5816500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5973200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5983700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5893800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6099700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>6036700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5841400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5587800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>5605900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>5755700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>5383100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>5114800</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>5166000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>4886300</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11163700</v>
+      </c>
+      <c r="E76" s="3">
         <v>11463600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11404500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10545000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9734700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9778000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9106600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8998200</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M76" s="3">
         <v>9100900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8741100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8262700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8276200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8071900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7689700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7215600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7132500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7322500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7209000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6842800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6655600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6511200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6500100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6275200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6324900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5725100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6408900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6805100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6754900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6577400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6678300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6694300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6486000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6315000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6446700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>6623400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>6272800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>5940500</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>5953600</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>5790300</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>580400</v>
+      </c>
+      <c r="E81" s="3">
         <v>591000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>471700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>501500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>514700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>485000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>298700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>409800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>349200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>406400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>226700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>327200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>386200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>368000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>288100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>346700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>305700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>309800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>288600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>316100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>185700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>175400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>170300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>27800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-167700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>51600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>237600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>286100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>294200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>305600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>268100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>294300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>289700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>307500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>315200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>367400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>277500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>268300</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>271100</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>287700</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>60100</v>
+      </c>
+      <c r="E83" s="3">
         <v>55600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>51900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>48300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>44900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>47100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>50000</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
         <v>44000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>43600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>44500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>44300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>48700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>46200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>46000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>44800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>51300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>46400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>43500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>44300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>43100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>44700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>46300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>42400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>30700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>48600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>50800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>36500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>25100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>33400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>34300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>34600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>22300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>33500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>35500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>34900</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>20100</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>34900</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1344300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-827500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5340800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>668600</v>
       </c>
-      <c r="G89" s="3">
-        <v>1715200</v>
-      </c>
       <c r="H89" s="3">
+        <v>1669000</v>
+      </c>
+      <c r="I89" s="3">
         <v>304500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-624400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>777300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-75000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>265500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-877500</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
         <v>827400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>317500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-136300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-283300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>829100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-163500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>219900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>185600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>84400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1795200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>4631800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>488400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>402000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>49800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>730200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>658300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-696200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-158800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>454900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>407100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>2065400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>269800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>499800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-66700</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-3841900</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>223500</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-17200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-26700</v>
       </c>
-      <c r="G91" s="3">
-        <v>-14200</v>
-      </c>
       <c r="H91" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="I91" s="3">
         <v>-23000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-21500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-37700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-40600</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R91" s="3">
         <v>-102800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-72800</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-17200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-599900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-17000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-13200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-10400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-12600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-9000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-20100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-9800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-16900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-5700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-15400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-25000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>2400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-5100</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-9700</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-19700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-81000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-72500</v>
       </c>
-      <c r="G94" s="3">
-        <v>-105900</v>
-      </c>
       <c r="H94" s="3">
+        <v>-58400</v>
+      </c>
+      <c r="I94" s="3">
         <v>-300400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-93200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>331100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-33500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-60100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1274500</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
         <v>-269600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-607900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>595500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>5600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2367800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>1616400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>1121900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1381000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>4240600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2665200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-949200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1138700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>316400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>161200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>276500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-615600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>39600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-33100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-17500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-8300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>159900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-22400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-11300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-529700</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,43 +10455,44 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G96" s="3">
-        <v>929600</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="D96" s="3">
+        <v>1165200</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3">
+        <v>898800</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3">
         <v>232300</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>727300</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3" t="s">
-        <v>5</v>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
       </c>
       <c r="O96" s="3" t="s">
         <v>5</v>
@@ -10266,8 +10500,8 @@
       <c r="P96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10279,11 +10513,11 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-108500</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -10291,11 +10525,11 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>623500</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -10303,38 +10537,38 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>418200</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-197600</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>309300</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>3000</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-12700</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>2600</v>
       </c>
-      <c r="AM96" s="3">
-        <v>0</v>
-      </c>
       <c r="AN96" s="3">
         <v>0</v>
       </c>
@@ -10344,8 +10578,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,174 +10953,180 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1875300</v>
+      </c>
+      <c r="E100" s="3">
         <v>1169800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>7350000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>61900</v>
       </c>
-      <c r="G100" s="3">
-        <v>-2139800</v>
-      </c>
       <c r="H100" s="3">
+        <v>-2141000</v>
+      </c>
+      <c r="I100" s="3">
         <v>-533700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1512900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1634900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1288000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1244300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>70700</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
         <v>286600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1728400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1960600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-539600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-624500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>326400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1694900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1861700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-4433100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>4200200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1035300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>730600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-747600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>458400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-573400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-28200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1055400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-623300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-3400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-893100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-944100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-928600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>200400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>982300</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>1323300</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-1443600</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-328000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-320900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>114000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-251000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>283300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-46400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-204800</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
         <v>-326100</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10894,18 +11143,18 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X101" s="3">
-        <v>0</v>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>530200</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
         <v>0</v>
       </c>
@@ -10913,25 +11162,25 @@
         <v>0</v>
       </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-72000</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
         <v>0</v>
       </c>
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>5</v>
+      <c r="AG101" s="3">
+        <v>0</v>
       </c>
       <c r="AH101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI101" s="3">
-        <v>0</v>
+      <c r="AI101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AJ101" s="3">
         <v>0</v>
@@ -10954,44 +11203,47 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-622500</v>
+      </c>
+      <c r="E102" s="3">
         <v>472500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1765500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>467500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-858400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-850600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>909300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2492300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1113200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1403300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>262800</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
         <v>0</v>
       </c>
@@ -10999,81 +11251,84 @@
         <v>0</v>
       </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>-547600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1437900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1501400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-817300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1406800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1779300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-353100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>666200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>422100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-260200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2647300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>80300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-101300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>669400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>460400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-13500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>547400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-389900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-494300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1048600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-681200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>688900</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>909000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-3185800</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-1237300</v>
       </c>
     </row>
